--- a/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:16:44+00:00</t>
+    <t>2025-02-11T12:34:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:34:01+00:00</t>
+    <t>2025-02-11T13:39:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:39:54+00:00</t>
+    <t>2025-02-11T16:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:00:38+00:00</t>
+    <t>2025-02-11T16:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:22:40+00:00</t>
+    <t>2025-02-12T08:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T08:22:12+00:00</t>
+    <t>2025-02-12T08:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/nr-snapshot-5/ig/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T08:44:28+00:00</t>
+    <t>2025-02-12T08:52:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
